--- a/stories/arbres/ATOM-FAM.VER.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Diane est dans le salon, près de papa. Papa plie du linge. Diane veut aider. Elle attrape le panier. Le panier glisse. Les chaussettes tombent. Diane a le ventre serré. Elle va vers papa. Diane dit : papa, le panier est tombé. J'ai fait tomber les chaussettes. Papa s'approche. Papa dit : merci de raconter. On ramasse ensemble. Diane prend une chaussette. Papa prend l'autre. Plus tard, dans la cuisine, Diane veut aider maman. Un verre d'eau penche. L'eau glisse. Diane va vers maman. Diane dit : maman, l'eau est tombée. Maman dit : merci de raconter. On essuie ensemble. Papa entre. Diane dit : papa, j'ai raconté. L'eau est tombée. Papa écoute. On raconte à papa ou maman. C'est comme ça. Diane se sent plus légère.</t>
+          <t>Diane est dans le salon, près de papa. Papa plie du linge. Diane veut aider. Elle attrape le panier. Le panier glisse. Les chaussettes tombent. Diane a le ventre serré. Elle va vers papa. Papa, le panier est tombé. J'ai fait tomber les chaussettes. Papa s'approche. Merci de raconter. On ramasse ensemble. Diane prend une chaussette. Papa prend l'autre. Plus tard, dans la cuisine, Diane veut aider maman. Un verre d'eau penche. L'eau glisse. Diane va vers maman. Maman, l'eau est tombée. Merci de raconter. On essuie ensemble. Papa entre. Papa, j'ai raconté. L'eau est tombée. Papa écoute. On raconte à papa ou maman. C'est comme ça. Diane se sent plus légère.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Diane est dans le salon, près de papa. Papa plie du linge. Diane veut aider. Elle attrape le panier. Le panier glisse. Les chaussettes tombent. Diane a le ventre serré. Elle va vers papa.
+enfant-f|Papa, le panier est tombé. J'ai fait tomber les chaussettes. Papa s'approche.
+papa|Merci de raconter. On ramasse ensemble.
+narrateur|Diane prend une chaussette. Papa prend l'autre. Plus tard, dans la cuisine, Diane veut aider maman. Un verre d'eau penche. L'eau glisse. Diane va vers maman.
+enfant-f|Maman, l'eau est tombée.
+maman|Merci de raconter. On essuie ensemble. Papa entre.
+enfant-f|Papa, j'ai raconté. L'eau est tombée. Papa écoute. On raconte à papa ou maman. C'est comme ça.
+narrateur|Diane se sent plus légère.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Les chaussettes sont tombées. Que fait Diane ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Diane a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le salon est rangé. La table est sèche. Diane se lave les mains.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Diane se sent plus légère.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Les chaussettes sont tombées. Que fait Diane ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Diane a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Le salon est rangé. La table est sèche. Diane se lave les mains.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.VER.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diane raconte à papa et maman</t>
+          <t>Chouchou raconte à papa et maman</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou fait tomber le panier de chaussettes. Il raconte à papa. Plus tard, de l'eau glisse. Il raconte à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Diane est dans le salon, près de papa. Papa plie du linge. Diane veut aider. Elle attrape le panier. Le panier glisse. Les chaussettes tombent. Diane a le ventre serré. Elle va vers papa. Papa, le panier est tombé. J'ai fait tomber les chaussettes. Papa s'approche. Merci de raconter. On ramasse ensemble. Diane prend une chaussette. Papa prend l'autre. Plus tard, dans la cuisine, Diane veut aider maman. Un verre d'eau penche. L'eau glisse. Diane va vers maman. Maman, l'eau est tombée. Merci de raconter. On essuie ensemble. Papa entre. Papa, j'ai raconté. L'eau est tombée. Papa écoute. On raconte à papa ou maman. C'est comme ça. Diane se sent plus légère.</t>
+          <t>Le panier de linge craque. Il sent le savon doux. Une serviette encore tiède dépasse. Des chaussettes font une petite pile. L'une est rouge. L'une est bleue. Le canapé a un plaid gris. Le plaid est rêche et chaud. Tu as senti le savon, Chouchou ? Oui, papa. Ça sent propre. Je plie le linge. Tu veux m'aider un peu ? Oui. Je veux aider. En ce moment, Chouchou tire le panier. Il est près de papa. Il attrape le panier. Le panier glisse. Les chaussettes tombent. Elles font un tas mou. Chouchou a le ventre serré. Il va vers papa. Papa, le panier est tombé. J'ai fait tomber les chaussettes. Je t'écoute, Chouchou. Merci de raconter. On ramasse ensemble. Tu as fait du bon travail. Tu prends la rouge. J'ai la bleue. D'accord. Chouchou prend une chaussette. Papa prend l'autre. Le panier se remplit à nouveau. On pose le panier plus près, hein ? Oui. Plus près. Plus tard, dans la cuisine, ça sent la soupe. Maman coupe une carotte. Un verre d'eau penche sur la table. Chouchou veut aider maman. L'eau glisse. Elle fait une petite rivière. Chouchou va vers maman. Maman, l'eau est tombée. J'ai raconté. Je t'écoute. Merci de raconter. On essuie ensemble. Bravo, Chouchou. C'est du bon travail. Papa entre. Papa, j'ai raconté. L'eau est tombée. Je t'écoute. On raconte à papa ou maman. C'est comme ça. Tu as su raconter encore. Oui. Chouchou se sent plus léger. Tu veux le torchon à carreaux ? Oui. Il est doux. La petite rivière d'eau part. La table redevient mate. La soupe fume encore. Tu veux rester près de moi ? Oui. Près de toi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1324,83 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Diane est dans le salon, près de papa. Papa plie du linge. Diane veut aider. Elle attrape le panier. Le panier glisse. Les chaussettes tombent. Diane a le ventre serré. Elle va vers papa.
-enfant-f|Papa, le panier est tombé. J'ai fait tomber les chaussettes. Papa s'approche.
-papa|Merci de raconter. On ramasse ensemble.
-narrateur|Diane prend une chaussette. Papa prend l'autre. Plus tard, dans la cuisine, Diane veut aider maman. Un verre d'eau penche. L'eau glisse. Diane va vers maman.
-enfant-f|Maman, l'eau est tombée.
-maman|Merci de raconter. On essuie ensemble. Papa entre.
-enfant-f|Papa, j'ai raconté. L'eau est tombée. Papa écoute. On raconte à papa ou maman. C'est comme ça.
-narrateur|Diane se sent plus légère.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le panier de linge craque.
+narrateur|Il sent le savon doux.
+narrateur|Une serviette encore tiède dépasse.
+narrateur|Des chaussettes font une petite pile.
+narrateur|L'une est rouge.
+narrateur|L'une est bleue.
+narrateur|Le canapé a un plaid gris.
+narrateur|Le plaid est rêche et chaud.
+papa|Tu as senti le savon, Chouchou ?
+enfant-m|Oui, papa.
+enfant-m|Ça sent propre.
+papa|Je plie le linge.
+papa|Tu veux m'aider un peu ?
+enfant-m|Oui.
+enfant-m|Je veux aider.
+narrateur|En ce moment, Chouchou tire le panier.
+narrateur|Il est près de papa.
+narrateur|Il attrape le panier.
+narrateur|Le panier glisse.
+narrateur|Les chaussettes tombent.
+narrateur|Elles font un tas mou.
+narrateur|Chouchou a le ventre serré.
+narrateur|Il va vers papa.
+enfant-m|Papa, le panier est tombé.
+enfant-m|J'ai fait tomber les chaussettes.
+papa|Je t'écoute, Chouchou.
+papa|Merci de raconter.
+papa|On ramasse ensemble.
+papa|Tu as fait du bon travail.
+papa|Tu prends la rouge.
+papa|J'ai la bleue.
+enfant-m|D'accord.
+narrateur|Chouchou prend une chaussette.
+narrateur|Papa prend l'autre.
+narrateur|Le panier se remplit à nouveau.
+papa|On pose le panier plus près, hein ?
+enfant-m|Oui.
+enfant-m|Plus près.
+narrateur|Plus tard, dans la cuisine, ça sent la soupe.
+narrateur|Maman coupe une carotte.
+narrateur|Un verre d'eau penche sur la table.
+narrateur|Chouchou veut aider maman.
+narrateur|L'eau glisse.
+narrateur|Elle fait une petite rivière.
+narrateur|Chouchou va vers maman.
+enfant-m|Maman, l'eau est tombée.
+enfant-m|J'ai raconté.
+maman|Je t'écoute.
+maman|Merci de raconter.
+maman|On essuie ensemble.
+maman|Bravo, Chouchou.
+maman|C'est du bon travail.
+narrateur|Papa entre.
+enfant-m|Papa, j'ai raconté.
+enfant-m|L'eau est tombée.
+papa|Je t'écoute.
+papa|On raconte à papa ou maman.
+papa|C'est comme ça.
+papa|Tu as su raconter encore.
+enfant-m|Oui.
+narrateur|Chouchou se sent plus léger.
+maman|Tu veux le torchon à carreaux ?
+enfant-m|Oui.
+enfant-m|Il est doux.
+narrateur|La petite rivière d'eau part.
+narrateur|La table redevient mate.
+maman|La soupe fume encore.
+maman|Tu veux rester près de moi ?
+enfant-m|Oui.
+enfant-m|Près de toi.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>panier_linge,verre_eau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,7 +1425,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Les chaussettes sont tombées. Que fait Diane ?</t>
+          <t>Les chaussettes sont tombées. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1581,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Les chaussettes sont tombées. Que fait Diane ?</t>
+          <t>narrateur|Les chaussettes sont tombées.
+narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1610,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Diane a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
+          <t>Chouchou a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Chouchou. J'ai raconté. Le panier, puis l'eau. Oui. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1754,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Diane a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
+          <t>narrateur|Chouchou a raconté.
+narrateur|Papa a écouté.
+narrateur|Maman a écouté.
+narrateur|Ensemble, ils ont ramassé.
+papa|Merci d'avoir raconté.
+maman|On raconte à papa ou maman.
+papa|Bravo, Chouchou.
+enfant-m|J'ai raconté.
+enfant-m|Le panier, puis l'eau.
+maman|Oui.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le salon est rangé. La table est sèche. Diane se lave les mains.</t>
+          <t>Le salon est rangé. La table est sèche. Chouchou se lave les mains. Tu veux rester près du panier ? Oui. Il sent le savon. La chaussette rouge est repliée. Et la bleue aussi. Le plaid gris redevient calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1932,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le salon est rangé. La table est sèche. Diane se lave les mains.</t>
+          <t>narrateur|Le salon est rangé.
+narrateur|La table est sèche.
+narrateur|Chouchou se lave les mains.
+maman|Tu veux rester près du panier ?
+enfant-m|Oui.
+enfant-m|Il sent le savon.
+papa|La chaussette rouge est repliée.
+enfant-m|Et la bleue aussi.
+narrateur|Le plaid gris redevient calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1968,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Tu as fait du bon travail. Le panier de linge ne craque plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2108,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai raconté.
+enfant-m|Papa et maman ont écouté.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le panier de linge ne craque plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2173,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le panier de linge craque. Il sent le savon doux. Une serviette encore tiède dépasse. Des chaussettes font une petite pile. L'une est rouge. L'une est bleue. Le canapé a un plaid gris. Le plaid est rêche et chaud. Tu as senti le savon, Chouchou ? Oui, papa. Ça sent propre. Je plie le linge. Tu veux m'aider un peu ? Oui. Je veux aider. En ce moment, Chouchou tire le panier. Il est près de papa. Il attrape le panier. Le panier glisse. Les chaussettes tombent. Elles font un tas mou. Chouchou a le ventre serré. Il va vers papa. Papa, le panier est tombé. J'ai fait tomber les chaussettes. Je t'écoute, Chouchou. Merci de raconter. On ramasse ensemble. Tu as fait du bon travail. Tu prends la rouge. J'ai la bleue. D'accord. Chouchou prend une chaussette. Papa prend l'autre. Le panier se remplit à nouveau. On pose le panier plus près, hein ? Oui. Plus près. Plus tard, dans la cuisine, ça sent la soupe. Maman coupe une carotte. Un verre d'eau penche sur la table. Chouchou veut aider maman. L'eau glisse. Elle fait une petite rivière. Chouchou va vers maman. Maman, l'eau est tombée. J'ai raconté. Je t'écoute. Merci de raconter. On essuie ensemble. Bravo, Chouchou. C'est du bon travail. Papa entre. Papa, j'ai raconté. L'eau est tombée. Je t'écoute. On raconte à papa ou maman. C'est comme ça. Tu as su raconter encore. Oui. Chouchou se sent plus léger. Tu veux le torchon à carreaux ? Oui. Il est doux. La petite rivière d'eau part. La table redevient mate. La soupe fume encore. Tu veux rester près de moi ? Oui. Près de toi.</t>
+          <t>Le panier de linge craque. Il sent le savon doux. Une serviette encore tiède dépasse. Des chaussettes font une petite pile. L'une est rouge. L'une est bleue. Le canapé a un plaid gris. Le plaid est rêche et chaud. Tu as senti le savon, Chouchou ? Oui, papa. Ça sent propre. Je plie le linge. Tu veux m'aider un peu ? Oui. Je veux aider. En ce moment, Chouchou tire le panier. Il est près de papa. Il attrape le panier. Le panier glisse. Les chaussettes tombent. Elles font un tas mou. Chouchou a le ventre serré. Il va vers papa. Papa, le panier est tombé. J'ai fait tomber les chaussettes. Je t'écoute, Chouchou. Merci de raconter. On ramasse ensemble. Tu prends la rouge. J'ai la bleue. D'accord. Chouchou prend une chaussette. Papa prend l'autre. Le panier se remplit à nouveau. On pose le panier plus près, hein ? Oui. Plus près. Plus tard, dans la cuisine, ça sent la soupe. Maman coupe une carotte. Un verre d'eau penche sur la table. Chouchou veut aider maman. L'eau glisse. Elle fait une petite rivière. Chouchou va vers maman. Maman, l'eau est tombée. J'ai raconté. Je t'écoute. Merci de raconter. On essuie ensemble. Bravo, Chouchou. Papa entre. Papa, j'ai raconté. L'eau est tombée. Je t'écoute. On raconte à papa ou maman. C'est comme ça. Tu as su raconter encore. Oui. Chouchou se sent plus léger. Tu veux le torchon à carreaux ? Oui. Il est doux. La petite rivière d'eau part. La table redevient mate. La soupe fume encore. Tu veux rester près de moi ? Oui. Près de toi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Diane est dans le salon, près de papa. Papa plie du linge. Diane veut aider. Elle attrape le panier. Le panier glisse. Les chaussettes tombent. Diane a le ventre serré. Elle va vers papa. Diane dit : papa, le panier est tombé. J'ai fait tomber les chaussettes. Papa s'approche. Papa dit : merci de &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. On ramasse ensemble. Diane prend une chaussette. Papa prend l'autre. Plus tard, dans la cuisine, Diane veut aider maman. Un verre d'eau penche. L'eau glisse. Diane va vers maman. Diane dit : maman, l'eau est tombée. Maman dit : merci de raconter. On essuie ensemble. Papa entre. Diane dit : papa, j'ai raconté. L'eau est tombée. Papa écoute. On raconte à papa ou maman. C'est comme ça. Diane se sent plus légère.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le panier de linge craque. Il sent le savon doux. Une serviette encore tiède dépasse. Des chaussettes font une petite pile. L'une est rouge. L'une est bleue. Le canapé a un plaid gris. Le plaid est rêche et chaud. Tu as senti le savon, Chouchou ? Oui, papa. Ça sent propre. Je plie le linge. Tu veux m'aider un peu ? Oui. Je veux aider. En ce moment, Chouchou tire le panier. Il est près de papa. Il attrape le panier. Le panier glisse. Les chaussettes tombent. Elles font un tas mou. Chouchou a le ventre serré. Il va vers papa. Papa, le panier est tombé. J'ai fait tomber les chaussettes. Je t'écoute, Chouchou. Merci de raconter. On ramasse ensemble. Tu prends la rouge. J'ai la bleue. D'accord. Chouchou prend une chaussette. Papa prend l'autre. Le panier se remplit à nouveau. On pose le panier plus près, hein ? Oui. Plus près. Plus tard, dans la cuisine, ça sent la soupe. Maman coupe une carotte. Un verre d'eau penche sur la table. Chouchou veut aider maman. L'eau glisse. Elle fait une petite rivière. Chouchou va vers maman. Maman, l'eau est tombée. J'ai raconté. Je t'écoute. Merci de raconter. On essuie ensemble. Bravo, Chouchou. Papa entre. Papa, j'ai raconté. L'eau est tombée. Je t'écoute. On raconte à papa ou maman. C'est comme ça. Tu as su raconter encore. Oui. Chouchou se sent plus léger. Tu veux le torchon à carreaux ? Oui. Il est doux. La petite rivière d'eau part. La table redevient mate. La soupe fume encore. Tu veux rester près de moi ? Oui. Près de toi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1352,7 +1352,6 @@
 papa|Je t'écoute, Chouchou.
 papa|Merci de raconter.
 papa|On ramasse ensemble.
-papa|Tu as fait du bon travail.
 papa|Tu prends la rouge.
 papa|J'ai la bleue.
 enfant-m|D'accord.
@@ -1375,7 +1374,6 @@
 maman|Merci de raconter.
 maman|On essuie ensemble.
 maman|Bravo, Chouchou.
-maman|C'est du bon travail.
 narrateur|Papa entre.
 enfant-m|Papa, j'ai raconté.
 enfant-m|L'eau est tombée.
@@ -1430,7 +1428,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Les chaussettes sont tombées. Que fait Diane ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les chaussettes sont tombées. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1585,7 +1583,6 @@
 narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1610,12 +1607,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Chouchou. J'ai raconté. Le panier, puis l'eau. Oui. C'est du bon travail.</t>
+          <t>Chouchou a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Chouchou. J'ai raconté. Le panier, puis l'eau. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Diane a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt; aide.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Chouchou. J'ai raconté. Le panier, puis l'eau. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1763,11 +1760,9 @@
 papa|Bravo, Chouchou.
 enfant-m|J'ai raconté.
 enfant-m|Le panier, puis l'eau.
-maman|Oui.
-maman|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1797,7 +1792,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le salon est rangé. La table est sèche. Diane se lave les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le salon est rangé. La table est sèche. Chouchou se lave les mains. Tu veux rester près du panier ? Oui. Il sent le savon. La chaussette rouge est repliée. Et la bleue aussi. Le plaid gris redevient calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1943,7 +1938,6 @@
 narrateur|Le plaid gris redevient calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1968,12 +1962,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Tu as fait du bon travail. Le panier de linge ne craque plus. L'histoire est finie.</t>
+          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Le panier de linge ne craque plus.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Le panier de linge ne craque plus.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2111,12 +2105,9 @@
           <t>enfant-m|J'ai raconté.
 enfant-m|Papa et maman ont écouté.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le panier de linge ne craque plus.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le panier de linge ne craque plus.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2135,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2180,6 +2171,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Diane, papa, maman</t>
+          <t>Chouchou, papa, maman</t>
         </is>
       </c>
     </row>
